--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="147" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BC0A5533-A6CC-43BB-A707-A07BDE94D69D}"/>
+  <xr:revisionPtr revIDLastSave="164" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA279308-1BB7-43B5-838D-A941ACC6648C}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -417,16 +417,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M9"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.77734375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.6328125" customWidth="1"/>
+    <col min="12" max="12" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -461,11 +462,11 @@
         <v>9</v>
       </c>
       <c r="M1">
-        <f>SUM(D2:D31)</f>
-        <v>351</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+        <f>SUM(D2:D32)</f>
+        <v>364</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45688</v>
       </c>
@@ -503,11 +504,11 @@
         <v>10</v>
       </c>
       <c r="M2">
-        <f>SUM(B2:B31)</f>
-        <v>187</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <f>SUM(B2:B32)</f>
+        <v>195</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45777</v>
       </c>
@@ -545,11 +546,11 @@
         <v>11</v>
       </c>
       <c r="M3">
-        <f>SUM(C2:C31)</f>
-        <v>164</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <f>SUM(C2:C32)</f>
+        <v>169</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45901</v>
       </c>
@@ -586,11 +587,11 @@
         <v>12</v>
       </c>
       <c r="M4">
-        <f>SUM(E2:E31)</f>
-        <v>156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+        <f>SUM(E2:E32)</f>
+        <v>162</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45962</v>
       </c>
@@ -627,11 +628,11 @@
         <v>13</v>
       </c>
       <c r="M5">
-        <f>SUM(F2:F31)</f>
-        <v>94</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <f>SUM(F2:F32)</f>
+        <v>97</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45992</v>
       </c>
@@ -666,11 +667,11 @@
         <v>14</v>
       </c>
       <c r="M6">
-        <f>SUM(G2:G31)</f>
-        <v>71</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+        <f>SUM(G2:G32)</f>
+        <v>74</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46023</v>
       </c>
@@ -701,8 +702,15 @@
       <c r="J7">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="L7" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7">
+        <f>SUM(I2:I32)</f>
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -733,26 +741,48 @@
       <c r="J8">
         <v>1</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L9" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9">
-        <f>SUM(I2:I31)</f>
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="L10" t="s">
+      <c r="L8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="M10">
-        <f>SUM(J2:J301)</f>
-        <v>17</v>
+      <c r="M8">
+        <f>SUM(J2:J302)</f>
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A9" s="1">
+        <v>46082</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+      <c r="C9">
+        <v>5</v>
+      </c>
+      <c r="D9">
+        <v>13</v>
+      </c>
+      <c r="E9">
+        <v>6</v>
+      </c>
+      <c r="F9">
+        <v>3</v>
+      </c>
+      <c r="G9">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>0</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="J9">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="164" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AA279308-1BB7-43B5-838D-A941ACC6648C}"/>
+  <xr:revisionPtr revIDLastSave="173" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2DD3633-1A48-45D5-B4BB-BEC3C125D449}"/>
   <bookViews>
-    <workbookView xWindow="-80" yWindow="-80" windowWidth="19360" windowHeight="11440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -487,18 +487,18 @@
         <v>64</v>
       </c>
       <c r="G2">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="I2">
         <f>D2-E2-F2-G2</f>
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="J2">
         <f>(I2-H2)</f>
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L2" t="s">
         <v>10</v>
@@ -539,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <f>(I3-H3)</f>
+        <f t="shared" ref="J3:J9" si="0">(I3-H3)</f>
         <v>2</v>
       </c>
       <c r="L3" t="s">
@@ -580,7 +580,7 @@
         <v>2</v>
       </c>
       <c r="J4">
-        <f t="shared" ref="J4:J5" si="0">(I4-H4)</f>
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L4" t="s">
@@ -611,18 +611,18 @@
         <v>1</v>
       </c>
       <c r="G5">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H5">
         <v>0</v>
       </c>
       <c r="I5">
         <f t="shared" ref="I5" si="1">D5-E5-F5-G5</f>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <f t="shared" si="0"/>
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -652,23 +652,24 @@
         <v>2</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6">
         <v>0</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
       <c r="L6" t="s">
         <v>14</v>
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>74</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -700,6 +701,7 @@
         <v>0</v>
       </c>
       <c r="J7">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
@@ -707,7 +709,7 @@
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
-        <v>28</v>
+        <v>30</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -739,6 +741,7 @@
         <v>1</v>
       </c>
       <c r="J8">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
@@ -746,7 +749,7 @@
       </c>
       <c r="M8">
         <f>SUM(J2:J302)</f>
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -778,6 +781,7 @@
         <v>1</v>
       </c>
       <c r="J9">
+        <f t="shared" si="0"/>
         <v>1</v>
       </c>
     </row>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -1,7 +1,7 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -59,12 +59,15 @@
     <t>3.rm_fulldecision</t>
   </si>
   <si>
+    <t>4.review_only</t>
+  </si>
+  <si>
+    <t>total_included</t>
+  </si>
+  <si>
     <t>total_meta</t>
   </si>
   <si>
-    <t>total_included</t>
-  </si>
-  <si>
     <t>TOTAL</t>
   </si>
   <si>
@@ -87,16 +90,13 @@
   </si>
   <si>
     <t>INCLUDED META</t>
-  </si>
-  <si>
-    <t>4.review_only</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,16 +418,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.45"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.90625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.6328125" customWidth="1"/>
-    <col min="12" max="12" width="23.453125" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" customWidth="1"/>
+    <col min="12" max="12" width="23.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -450,23 +450,23 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="I1" t="s">
         <v>8</v>
       </c>
       <c r="J1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L1" s="2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
         <v>364</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13">
       <c r="A2" s="1">
         <v>45688</v>
       </c>
@@ -501,14 +501,14 @@
         <v>12</v>
       </c>
       <c r="L2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:13">
       <c r="A3" s="1">
         <v>45777</v>
       </c>
@@ -543,14 +543,14 @@
         <v>2</v>
       </c>
       <c r="L3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:13">
       <c r="A4" s="1">
         <v>45901</v>
       </c>
@@ -584,14 +584,14 @@
         <v>1</v>
       </c>
       <c r="L4" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:13">
       <c r="A5" s="1">
         <v>45962</v>
       </c>
@@ -625,14 +625,14 @@
         <v>0</v>
       </c>
       <c r="L5" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:13">
       <c r="A6" s="1">
         <v>45992</v>
       </c>
@@ -665,14 +665,14 @@
         <v>2</v>
       </c>
       <c r="L6" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:13">
       <c r="A7" s="1">
         <v>46023</v>
       </c>
@@ -705,14 +705,14 @@
         <v>0</v>
       </c>
       <c r="L7" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:13">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -745,14 +745,14 @@
         <v>1</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="M8">
         <f>SUM(J2:J302)</f>
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:13">
       <c r="A9" s="1">
         <v>46082</v>
       </c>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29825"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="173" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2DD3633-1A48-45D5-B4BB-BEC3C125D449}"/>
+  <xr:revisionPtr revIDLastSave="181" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2931A9DA-EB61-4156-BACA-B661FF05BB84}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -96,7 +96,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -418,16 +418,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.45"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5703125" customWidth="1"/>
-    <col min="12" max="12" width="23.42578125" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
+    <col min="12" max="12" width="23.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -466,7 +466,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="2" spans="1:13">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>45688</v>
       </c>
@@ -508,7 +508,7 @@
         <v>195</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>45777</v>
       </c>
@@ -550,7 +550,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="4" spans="1:13">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>45901</v>
       </c>
@@ -571,7 +571,7 @@
         <v>17</v>
       </c>
       <c r="G4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H4">
         <v>1</v>
@@ -591,7 +591,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:13">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>45962</v>
       </c>
@@ -632,7 +632,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="6" spans="1:13">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>45992</v>
       </c>
@@ -669,10 +669,10 @@
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>76</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>46023</v>
       </c>
@@ -712,7 +712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:13">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -752,7 +752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>46082</v>
       </c>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="181" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2931A9DA-EB61-4156-BACA-B661FF05BB84}"/>
+  <xr:revisionPtr revIDLastSave="190" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95ADAD68-5BA5-4AB7-B2D5-466DEC590D52}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -417,17 +417,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M10"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.5546875" customWidth="1"/>
-    <col min="12" max="12" width="23.44140625" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.08984375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.90625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.54296875" customWidth="1"/>
+    <col min="12" max="12" width="23.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -463,10 +463,10 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>364</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+        <v>381</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A2" s="1">
         <v>45688</v>
       </c>
@@ -505,10 +505,10 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>195</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A3" s="1">
         <v>45777</v>
       </c>
@@ -539,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J9" si="0">(I3-H3)</f>
+        <f t="shared" ref="J3:J10" si="0">(I3-H3)</f>
         <v>2</v>
       </c>
       <c r="L3" t="s">
@@ -547,10 +547,10 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>169</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A4" s="1">
         <v>45901</v>
       </c>
@@ -591,7 +591,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A5" s="1">
         <v>45962</v>
       </c>
@@ -629,10 +629,10 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A6" s="1">
         <v>45992</v>
       </c>
@@ -672,7 +672,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A7" s="1">
         <v>46023</v>
       </c>
@@ -712,7 +712,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A8" s="1">
         <v>46054</v>
       </c>
@@ -752,7 +752,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
       <c r="A9" s="1">
         <v>46082</v>
       </c>
@@ -783,6 +783,39 @@
       <c r="J9">
         <f t="shared" si="0"/>
         <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A10" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B10">
+        <v>15</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>17</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10">
+        <v>17</v>
+      </c>
+      <c r="G10">
+        <v>0</v>
+      </c>
+      <c r="H10">
+        <v>0</v>
+      </c>
+      <c r="I10">
+        <v>0</v>
+      </c>
+      <c r="J10">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="190" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{95ADAD68-5BA5-4AB7-B2D5-466DEC590D52}"/>
+  <xr:revisionPtr revIDLastSave="203" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BF0C07-D3EC-4A9B-92EF-6E1DF6B7D2AA}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:M11"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>381</v>
+        <v>418</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>210</v>
+        <v>230</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -539,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J10" si="0">(I3-H3)</f>
+        <f t="shared" ref="J3:J11" si="0">(I3-H3)</f>
         <v>2</v>
       </c>
       <c r="L3" t="s">
@@ -547,7 +547,7 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>171</v>
+        <v>188</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -561,7 +561,7 @@
         <v>25</v>
       </c>
       <c r="D4">
-        <f>SUM(B4,C4)</f>
+        <f t="shared" ref="D4:D10" si="1">B4+C4</f>
         <v>47</v>
       </c>
       <c r="E4">
@@ -588,7 +588,7 @@
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
-        <v>162</v>
+        <v>175</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -602,6 +602,7 @@
         <v>6</v>
       </c>
       <c r="D5">
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E5">
@@ -617,7 +618,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <f t="shared" ref="I5" si="1">D5-E5-F5-G5</f>
+        <f t="shared" ref="I5" si="2">D5-E5-F5-G5</f>
         <v>0</v>
       </c>
       <c r="J5">
@@ -629,7 +630,7 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>114</v>
+        <v>132</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -643,6 +644,7 @@
         <v>0</v>
       </c>
       <c r="D6">
+        <f t="shared" si="1"/>
         <v>6</v>
       </c>
       <c r="E6">
@@ -669,7 +671,7 @@
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>75</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -683,6 +685,7 @@
         <v>7</v>
       </c>
       <c r="D7">
+        <f t="shared" si="1"/>
         <v>16</v>
       </c>
       <c r="E7">
@@ -709,7 +712,7 @@
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
-        <v>30</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -723,6 +726,7 @@
         <v>3</v>
       </c>
       <c r="D8">
+        <f t="shared" si="1"/>
         <v>9</v>
       </c>
       <c r="E8">
@@ -749,7 +753,7 @@
       </c>
       <c r="M8">
         <f>SUM(J2:J302)</f>
-        <v>19</v>
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -763,6 +767,7 @@
         <v>5</v>
       </c>
       <c r="D9">
+        <f t="shared" si="1"/>
         <v>13</v>
       </c>
       <c r="E9">
@@ -796,6 +801,7 @@
         <v>2</v>
       </c>
       <c r="D10">
+        <f t="shared" si="1"/>
         <v>17</v>
       </c>
       <c r="E10">
@@ -816,6 +822,40 @@
       <c r="J10">
         <f t="shared" si="0"/>
         <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A11" s="1">
+        <v>46143</v>
+      </c>
+      <c r="B11">
+        <v>20</v>
+      </c>
+      <c r="C11">
+        <v>17</v>
+      </c>
+      <c r="D11">
+        <f>B11+C11</f>
+        <v>37</v>
+      </c>
+      <c r="E11">
+        <v>13</v>
+      </c>
+      <c r="F11">
+        <v>18</v>
+      </c>
+      <c r="G11">
+        <v>3</v>
+      </c>
+      <c r="H11">
+        <v>0</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="J11">
+        <f t="shared" si="0"/>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="203" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{43BF0C07-D3EC-4A9B-92EF-6E1DF6B7D2AA}"/>
+  <xr:revisionPtr revIDLastSave="212" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA21FCD7-4AC4-45E5-A21E-091174A33684}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M11"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>418</v>
+        <v>454</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>230</v>
+        <v>258</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -539,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J11" si="0">(I3-H3)</f>
+        <f t="shared" ref="J3:J12" si="0">(I3-H3)</f>
         <v>2</v>
       </c>
       <c r="L3" t="s">
@@ -547,7 +547,7 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>188</v>
+        <v>196</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -588,7 +588,7 @@
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -630,7 +630,7 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>132</v>
+        <v>155</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -671,7 +671,7 @@
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>78</v>
+        <v>82</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -712,7 +712,7 @@
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -856,6 +856,40 @@
       <c r="J11">
         <f t="shared" si="0"/>
         <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A12" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B12">
+        <v>28</v>
+      </c>
+      <c r="C12">
+        <v>8</v>
+      </c>
+      <c r="D12">
+        <f>B12+C12</f>
+        <v>36</v>
+      </c>
+      <c r="E12">
+        <v>7</v>
+      </c>
+      <c r="F12">
+        <v>23</v>
+      </c>
+      <c r="G12">
+        <v>4</v>
+      </c>
+      <c r="H12">
+        <v>2</v>
+      </c>
+      <c r="I12">
+        <v>2</v>
+      </c>
+      <c r="J12">
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="212" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA21FCD7-4AC4-45E5-A21E-091174A33684}"/>
+  <xr:revisionPtr revIDLastSave="219" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6FD441-89AC-4E14-95E2-34276B66B963}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -417,7 +417,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M17"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="10.90625" bestFit="1" customWidth="1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>454</v>
+        <v>502</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>258</v>
+        <v>298</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -547,7 +547,7 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>196</v>
+        <v>202</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -588,7 +588,7 @@
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
-        <v>182</v>
+        <v>193</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -630,7 +630,7 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>155</v>
+        <v>182</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -889,6 +889,50 @@
       </c>
       <c r="J12">
         <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A13" s="1">
+        <v>46204</v>
+      </c>
+      <c r="B13">
+        <v>40</v>
+      </c>
+      <c r="C13">
+        <v>6</v>
+      </c>
+      <c r="D13">
+        <v>48</v>
+      </c>
+      <c r="E13">
+        <v>11</v>
+      </c>
+      <c r="F13">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D14">
+        <f t="shared" ref="D14:D17" si="3">B14+C14</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D15">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="D16">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="D17">
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="219" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D6FD441-89AC-4E14-95E2-34276B66B963}"/>
+  <xr:revisionPtr revIDLastSave="237" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A0D692F-62B2-49A3-9201-B3EF88FC8E2C}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>502</v>
+        <v>539</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>298</v>
+        <v>326</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -539,7 +539,7 @@
         <v>5</v>
       </c>
       <c r="J3">
-        <f t="shared" ref="J3:J12" si="0">(I3-H3)</f>
+        <f t="shared" ref="J3:J17" si="0">(I3-H3)</f>
         <v>2</v>
       </c>
       <c r="L3" t="s">
@@ -547,7 +547,7 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>202</v>
+        <v>211</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -588,7 +588,7 @@
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
-        <v>193</v>
+        <v>200</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -630,7 +630,7 @@
       </c>
       <c r="M5">
         <f>SUM(F2:F32)</f>
-        <v>182</v>
+        <v>203</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.35">
@@ -671,7 +671,7 @@
       </c>
       <c r="M6">
         <f>SUM(G2:G32)</f>
-        <v>82</v>
+        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.35">
@@ -712,7 +712,7 @@
       </c>
       <c r="M7">
         <f>SUM(I2:I32)</f>
-        <v>35</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.35">
@@ -753,7 +753,7 @@
       </c>
       <c r="M8">
         <f>SUM(J2:J302)</f>
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.35">
@@ -911,11 +911,52 @@
       <c r="F13">
         <v>27</v>
       </c>
+      <c r="G13">
+        <v>7</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>3</v>
+      </c>
+      <c r="J13">
+        <f t="shared" si="0"/>
+        <v>2</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A14" s="1">
+        <v>46235</v>
+      </c>
+      <c r="B14">
+        <v>28</v>
+      </c>
+      <c r="C14">
+        <v>9</v>
+      </c>
       <c r="D14">
         <f t="shared" ref="D14:D17" si="3">B14+C14</f>
-        <v>0</v>
+        <v>37</v>
+      </c>
+      <c r="E14">
+        <v>7</v>
+      </c>
+      <c r="F14">
+        <v>21</v>
+      </c>
+      <c r="G14">
+        <v>4</v>
+      </c>
+      <c r="H14">
+        <v>3</v>
+      </c>
+      <c r="I14">
+        <v>5</v>
+      </c>
+      <c r="J14">
+        <f t="shared" si="0"/>
+        <v>2</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
@@ -923,16 +964,28 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
+      <c r="J15">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.35">
       <c r="D16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-    </row>
-    <row r="17" spans="4:4" x14ac:dyDescent="0.35">
+      <c r="J16">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="4:10" x14ac:dyDescent="0.35">
       <c r="D17">
         <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="J17">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>

--- a/materials/search_results_history.xlsx
+++ b/materials/search_results_history.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://unipdit-my.sharepoint.com/personal/tommaso_feraco_unipd_it/Documents/BESSI/living_SEB_review/materials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="237" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A0D692F-62B2-49A3-9201-B3EF88FC8E2C}"/>
+  <xr:revisionPtr revIDLastSave="241" documentId="11_AD4D5CB4E552A5DACE1C647E305F51585ADEDD82" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{161925EB-BA47-4DB9-A4C1-713D9970B621}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="29295" yWindow="2205" windowWidth="14400" windowHeight="11880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -463,7 +463,7 @@
       </c>
       <c r="M1">
         <f>SUM(D2:D32)</f>
-        <v>539</v>
+        <v>569</v>
       </c>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.35">
@@ -505,7 +505,7 @@
       </c>
       <c r="M2">
         <f>SUM(B2:B32)</f>
-        <v>326</v>
+        <v>347</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.35">
@@ -547,7 +547,7 @@
       </c>
       <c r="M3">
         <f>SUM(C2:C32)</f>
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.35">
@@ -588,7 +588,7 @@
       </c>
       <c r="M4">
         <f>SUM(E2:E32)</f>
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.35">
@@ -960,9 +960,21 @@
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.35">
+      <c r="A15" s="1">
+        <v>46266</v>
+      </c>
+      <c r="B15">
+        <v>21</v>
+      </c>
+      <c r="C15">
+        <v>9</v>
+      </c>
       <c r="D15">
         <f t="shared" si="3"/>
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c r="E15">
+        <v>6</v>
       </c>
       <c r="J15">
         <f t="shared" si="0"/>
